--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.00872958562804</v>
+        <v>3.738918557664556</v>
       </c>
       <c r="D2" t="n">
-        <v>22.92854401028038</v>
+        <v>3.725888401670562</v>
       </c>
       <c r="E2" t="n">
-        <v>7.940356727808025</v>
+        <v>1.290307968268804</v>
       </c>
       <c r="F2" t="n">
-        <v>7.905533206519485</v>
+        <v>1.284649146059416</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.901583708677476</v>
+        <v>0.4715073526600899</v>
       </c>
       <c r="D3" t="n">
-        <v>2.999423845465338</v>
+        <v>0.4874063748881175</v>
       </c>
       <c r="E3" t="n">
-        <v>7.940356727808025</v>
+        <v>1.290307968268804</v>
       </c>
       <c r="F3" t="n">
-        <v>7.905533206519485</v>
+        <v>1.284649146059416</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.77281629221616</v>
+        <v>3.375582647485126</v>
       </c>
       <c r="D4" t="n">
-        <v>20.73234724525973</v>
+        <v>3.369006427354706</v>
       </c>
       <c r="E4" t="n">
-        <v>7.940356727808025</v>
+        <v>1.290307968268804</v>
       </c>
       <c r="F4" t="n">
-        <v>7.905533206519485</v>
+        <v>1.284649146059416</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.22492690298829</v>
+        <v>2.799050621735597</v>
       </c>
       <c r="D5" t="n">
-        <v>17.25291997905703</v>
+        <v>2.803599496596768</v>
       </c>
       <c r="E5" t="n">
-        <v>7.940356727808025</v>
+        <v>1.290307968268804</v>
       </c>
       <c r="F5" t="n">
-        <v>7.905533206519485</v>
+        <v>1.284649146059416</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.34967497751633</v>
+        <v>4.119322183846404</v>
       </c>
       <c r="D6" t="n">
-        <v>25.43244391415091</v>
+        <v>4.132772136049524</v>
       </c>
       <c r="E6" t="n">
-        <v>7.940356727808025</v>
+        <v>1.290307968268804</v>
       </c>
       <c r="F6" t="n">
-        <v>7.905533206519485</v>
+        <v>1.284649146059416</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
